--- a/data/ugyfelek_adat.xlsx
+++ b/data/ugyfelek_adat.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/595ecd328626fcde/munka/ugyfelek/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{E8C6EC21-E844-4967-91C2-3ADAEC31A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BE32FFA-6011-49EE-92FC-1FF9DA0D29BC}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="8_{E8C6EC21-E844-4967-91C2-3ADAEC31A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0BD71B2-232A-42D1-9650-84AC08660476}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="18000" windowHeight="9360" xr2:uid="{66F20849-4EC5-42B8-B876-1042B778AFA7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{66F20849-4EC5-42B8-B876-1042B778AFA7}"/>
   </bookViews>
   <sheets>
     <sheet name="ugyfelek_adat" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="124">
   <si>
     <t>Id</t>
   </si>
@@ -327,14 +327,94 @@
   </si>
   <si>
     <t>+36309494078</t>
+  </si>
+  <si>
+    <t>Lefor Ádám</t>
+  </si>
+  <si>
+    <t>6726 Szeged Hargitai utca 36</t>
+  </si>
+  <si>
+    <t>1/60</t>
+  </si>
+  <si>
+    <t>adamlefor@gmail.com</t>
+  </si>
+  <si>
+    <t>+36307207521</t>
+  </si>
+  <si>
+    <t>Kenderesi Judit</t>
+  </si>
+  <si>
+    <t>kenderesijudit@gmail.com</t>
+  </si>
+  <si>
+    <t>+36</t>
+  </si>
+  <si>
+    <t>Meszlényiné Margó</t>
+  </si>
+  <si>
+    <t>Derkovits fasor 90</t>
+  </si>
+  <si>
+    <t>B.ép 2.a.</t>
+  </si>
+  <si>
+    <t>meszlenyine.kollarmargo@gmail.com</t>
+  </si>
+  <si>
+    <t>+36203280286</t>
+  </si>
+  <si>
+    <t>Ocsovszki Imre</t>
+  </si>
+  <si>
+    <t>Bajcsy-Zsilinszky u. 22</t>
+  </si>
+  <si>
+    <t>imre@esztimer.hu</t>
+  </si>
+  <si>
+    <t>+36 70 708 9196</t>
+  </si>
+  <si>
+    <t>Kovalcsik Ktalin</t>
+  </si>
+  <si>
+    <t>Szeged, Bartok tér 5</t>
+  </si>
+  <si>
+    <t>csikisz10@gmail.com</t>
+  </si>
+  <si>
+    <t>Bálint Zsófia</t>
+  </si>
+  <si>
+    <t>Selmeci utca 13</t>
+  </si>
+  <si>
+    <t>balint.zsofi97@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endrődy Judit </t>
+  </si>
+  <si>
+    <t>endrody.j@gmail.com</t>
+  </si>
+  <si>
+    <t>Attila utca 16.</t>
+  </si>
+  <si>
+    <t>1 emelet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -776,100 +856,58 @@
     </border>
   </borders>
   <cellStyleXfs count="43">
-    <xf fontId="1" fillId="10" borderId="0"/>
-    <xf fontId="1" fillId="14" borderId="0"/>
-    <xf fontId="1" fillId="18" borderId="0"/>
-    <xf fontId="1" fillId="22" borderId="0"/>
-    <xf fontId="1" fillId="26" borderId="0"/>
-    <xf fontId="1" fillId="30" borderId="0"/>
-    <xf fontId="1" fillId="11" borderId="0"/>
-    <xf fontId="1" fillId="15" borderId="0"/>
-    <xf fontId="1" fillId="19" borderId="0"/>
-    <xf fontId="1" fillId="23" borderId="0"/>
-    <xf fontId="1" fillId="27" borderId="0"/>
-    <xf fontId="1" fillId="31" borderId="0"/>
-    <xf fontId="1" fillId="12" borderId="0"/>
-    <xf fontId="1" fillId="16" borderId="0"/>
-    <xf fontId="1" fillId="20" borderId="0"/>
-    <xf fontId="1" fillId="24" borderId="0"/>
-    <xf fontId="1" fillId="28" borderId="0"/>
-    <xf fontId="1" fillId="32" borderId="0"/>
-    <xf fontId="9" fillId="5" borderId="4"/>
-    <xf fontId="2" fillId="0" borderId="0"/>
-    <xf fontId="3" fillId="0" borderId="1"/>
-    <xf fontId="4" fillId="0" borderId="2"/>
-    <xf fontId="5" fillId="0" borderId="3"/>
-    <xf fontId="5" fillId="0" borderId="0"/>
-    <xf fontId="13" fillId="7" borderId="7"/>
-    <xf fontId="14" fillId="0" borderId="0"/>
-    <xf fontId="18" fillId="10" borderId="0"/>
-    <xf fontId="12" fillId="0" borderId="6"/>
-    <xf fontId="1" fillId="8" borderId="8"/>
-    <xf fontId="17" fillId="9" borderId="0"/>
-    <xf fontId="17" fillId="13" borderId="0"/>
-    <xf fontId="17" fillId="17" borderId="0"/>
-    <xf fontId="17" fillId="21" borderId="0"/>
-    <xf fontId="17" fillId="25" borderId="0"/>
-    <xf fontId="17" fillId="29" borderId="0"/>
-    <xf fontId="6" fillId="2" borderId="0"/>
-    <xf fontId="10" fillId="6" borderId="5"/>
-    <xf fontId="15" fillId="0" borderId="0"/>
-    <xf fontId="0" fillId="10" borderId="0"/>
-    <xf fontId="16" fillId="0" borderId="9"/>
-    <xf fontId="7" fillId="3" borderId="0"/>
-    <xf fontId="8" fillId="4" borderId="0"/>
-    <xf fontId="11" fillId="6" borderId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
-    <xf fontId="1" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf fontId="1" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="1"/>
-    <xf fontId="1" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="2"/>
-    <xf fontId="1" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="3"/>
-    <xf fontId="1" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="4"/>
-    <xf fontId="1" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="5"/>
-    <xf fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="6"/>
-    <xf fontId="1" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="7"/>
-    <xf fontId="1" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="8"/>
-    <xf fontId="1" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="9"/>
-    <xf fontId="1" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="10"/>
-    <xf fontId="1" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="11"/>
-    <xf fontId="1" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="12"/>
-    <xf fontId="1" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="13"/>
-    <xf fontId="1" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="14"/>
-    <xf fontId="1" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="15"/>
-    <xf fontId="1" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="16"/>
-    <xf fontId="1" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="17"/>
-    <xf fontId="9" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" xfId="18"/>
-    <xf fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="19"/>
-    <xf fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="20"/>
-    <xf fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="21"/>
-    <xf fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="22"/>
-    <xf fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="23"/>
-    <xf fontId="13" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" xfId="24"/>
-    <xf fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="25"/>
-    <xf fontId="18" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26"/>
-    <xf fontId="12" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="27"/>
-    <xf fontId="1" applyFont="1" fillId="8" applyFill="1" borderId="8" applyBorder="1" xfId="28"/>
-    <xf fontId="17" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="29"/>
-    <xf fontId="17" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="30"/>
-    <xf fontId="17" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="31"/>
-    <xf fontId="17" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="32"/>
-    <xf fontId="17" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="33"/>
-    <xf fontId="17" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="34"/>
-    <xf fontId="6" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="35"/>
-    <xf fontId="10" applyFont="1" fillId="6" applyFill="1" borderId="5" applyBorder="1" xfId="36"/>
-    <xf fontId="15" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="37"/>
-    <xf fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="38"/>
-    <xf fontId="16" applyFont="1" fillId="0" applyFill="1" borderId="9" applyBorder="1" xfId="39"/>
-    <xf fontId="7" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="40"/>
-    <xf fontId="8" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="41"/>
-    <xf fontId="11" applyFont="1" fillId="6" applyFill="1" borderId="4" applyBorder="1" xfId="42"/>
-    <xf fontId="1" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
-    <xf fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="38"/>
-    <xf fontId="1" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="38"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="26"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="20% - 1. jelölőszín" xfId="0" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 1. jelölőszín" xfId="42" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 2. jelölőszín" xfId="1" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 3. jelölőszín" xfId="2" builtinId="38" customBuiltin="1"/>
     <cellStyle name="20% - 4. jelölőszín" xfId="3" builtinId="42" customBuiltin="1"/>
@@ -907,11 +945,11 @@
     <cellStyle name="Jó" xfId="35" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Kimenet" xfId="36" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Magyarázó szöveg" xfId="37" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Normál" xfId="38" builtinId="0"/>
-    <cellStyle name="Összesen" xfId="39" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Rossz" xfId="40" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Semleges" xfId="41" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Számítás" xfId="42" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Normál" xfId="0" builtinId="0"/>
+    <cellStyle name="Összesen" xfId="38" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Rossz" xfId="39" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Semleges" xfId="40" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Számítás" xfId="41" builtinId="22" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -924,6 +962,26 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E04BEC9-A6A9-4700-BB84-8D7EEEAA9D6D}" name="Táblázat1" displayName="Táblázat1" ref="A1:G34" totalsRowShown="0">
+  <autoFilter ref="A1:G34" xr:uid="{4E04BEC9-A6A9-4700-BB84-8D7EEEAA9D6D}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{20F74619-F6C6-402B-976F-3EB6D6C2561B}" name="Id"/>
+    <tableColumn id="2" xr3:uid="{141F81C0-34A9-4FDB-B97E-1F75C52CCC3F}" name="Név"/>
+    <tableColumn id="3" xr3:uid="{5DEF5317-4F68-433A-888C-C89E1156F460}" name="Város"/>
+    <tableColumn id="4" xr3:uid="{3FFD24C3-2F1D-4499-B608-BCFEB9806A10}" name="Lakcím"/>
+    <tableColumn id="5" xr3:uid="{6FC3B88F-06E7-4E21-9E0F-1F57CEAEB53D}" name="Emelet, ajtó"/>
+    <tableColumn id="6" xr3:uid="{5C8B48F6-BE6C-456A-892E-AFCC902991A0}" name="Email"/>
+    <tableColumn id="7" xr3:uid="{63C4A398-CD6F-467C-9D21-D72240A3BA86}" name="Tel"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1243,599 +1301,745 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D74237-402A-451B-B92A-B4098F765610}">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="1" width="2.7109375" customWidth="1" style="45"/>
-    <col min="2" max="2" bestFit="1" width="19" customWidth="1" style="45"/>
-    <col min="3" max="3" bestFit="1" width="14.42578125" customWidth="1" style="45"/>
-    <col min="4" max="4" bestFit="1" width="21.5703125" customWidth="1" style="45"/>
-    <col min="5" max="5" bestFit="1" width="10.85546875" customWidth="1" style="45"/>
-    <col min="6" max="6" bestFit="1" width="25.85546875" customWidth="1" style="45"/>
-    <col min="7" max="7" bestFit="1" width="13.42578125" customWidth="1" style="45"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="44">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="44" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="44" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="44">
+      <c r="G2" s="2">
         <v>36308415372</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="44">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="44">
+      <c r="G3" s="2">
         <v>36204446001</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="44">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="2">
         <v>36202309780</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="44">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="2">
         <v>36309595631</v>
       </c>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="44">
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="2">
         <v>36307225044</v>
       </c>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="44">
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44" t="s">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="2">
         <v>36307260808</v>
       </c>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="44">
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44" t="s">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="2">
         <v>36306557189</v>
       </c>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="44"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="44">
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44" t="s">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="2">
         <v>36301355402</v>
       </c>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="44"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="44">
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="44" t="s">
+      <c r="G10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="44">
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="44" t="s">
+      <c r="F11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="44">
+      <c r="G11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="2">
         <v>36205175033</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="44">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="2">
         <v>36202799322</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="44">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="F14" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="2">
         <v>36305869332</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="44">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="2">
         <v>36304001670</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="44">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="F16" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G16" s="2">
         <v>36308838715</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="44">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="F17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="2">
         <v>36703134683</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="44">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="44" t="s">
+      <c r="C18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="2">
         <v>36308503919</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="44">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="44" t="s">
+      <c r="D19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="2">
         <v>36303332466</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="44">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="2">
         <v>36303332466</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="44">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="44" t="s">
+      <c r="B21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="44" t="s">
+      <c r="D21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G21" s="44">
+      <c r="G21" s="2">
         <v>36709679051</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="44">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="C22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="44" t="s">
+      <c r="E22" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F22" s="44" t="s">
+      <c r="F22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G22" s="44" t="s">
+      <c r="G22" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="44">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="44" t="s">
+      <c r="B23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44" t="s">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="44" t="s">
+      <c r="G23" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="44">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="44" t="s">
+      <c r="E24" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="44" t="s">
+      <c r="F24" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G24" s="44" t="s">
+      <c r="G24" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="44">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="44" t="s">
+      <c r="B25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="44" t="s">
+      <c r="C25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44" t="s">
+      <c r="E25" s="2"/>
+      <c r="F25" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="44" t="s">
+      <c r="G25" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="44">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="B26" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="44" t="s">
+      <c r="C26" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="44" t="s">
+      <c r="D26" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="44" t="s">
+      <c r="E26" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F26" s="44" t="s">
+      <c r="F26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="44" t="s">
+      <c r="G26" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="44">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="44" t="s">
+      <c r="B27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44" t="s">
+      <c r="E27" s="2"/>
+      <c r="F27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G27" s="44" t="s">
+      <c r="G27" s="2" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>996</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G33" s="2">
+        <v>3630777777</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>997</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" s="2">
+        <v>36202130597</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F12" r:id="rId15"/>
-    <hyperlink ref="F17" r:id="rId16"/>
-    <hyperlink ref="F21" r:id="rId17"/>
+    <hyperlink ref="F12" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F17" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F21" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/ugyfelek_adat.xlsx
+++ b/data/ugyfelek_adat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/595ecd328626fcde/munka/ugyfelek/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{E8C6EC21-E844-4967-91C2-3ADAEC31A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0BD71B2-232A-42D1-9650-84AC08660476}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="8_{E8C6EC21-E844-4967-91C2-3ADAEC31A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E817F8E3-E009-44D1-8BBC-6F1727CEBB7C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{66F20849-4EC5-42B8-B876-1042B778AFA7}"/>
+    <workbookView xWindow="1170" yWindow="1275" windowWidth="21000" windowHeight="11625" xr2:uid="{66F20849-4EC5-42B8-B876-1042B778AFA7}"/>
   </bookViews>
   <sheets>
     <sheet name="ugyfelek_adat" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="129">
   <si>
     <t>Id</t>
   </si>
@@ -380,13 +380,16 @@
     <t>+36 70 708 9196</t>
   </si>
   <si>
-    <t>Kovalcsik Ktalin</t>
-  </si>
-  <si>
-    <t>Szeged, Bartok tér 5</t>
-  </si>
-  <si>
-    <t>csikisz10@gmail.com</t>
+    <t xml:space="preserve">Endrődy Judit </t>
+  </si>
+  <si>
+    <t>Attila utca 16.</t>
+  </si>
+  <si>
+    <t>1 emelet</t>
+  </si>
+  <si>
+    <t>endrody.j@gmail.com</t>
   </si>
   <si>
     <t>Bálint Zsófia</t>
@@ -398,23 +401,35 @@
     <t>balint.zsofi97@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Endrődy Judit </t>
-  </si>
-  <si>
-    <t>endrody.j@gmail.com</t>
-  </si>
-  <si>
-    <t>Attila utca 16.</t>
-  </si>
-  <si>
-    <t>1 emelet</t>
+    <t>Oroszlámos Timea</t>
+  </si>
+  <si>
+    <t>Sopron</t>
+  </si>
+  <si>
+    <t>timea.oroszlamos@gmail.com</t>
+  </si>
+  <si>
+    <t>Fábián Ildikó</t>
+  </si>
+  <si>
+    <t>Gerle utca</t>
+  </si>
+  <si>
+    <t>88/a</t>
+  </si>
+  <si>
+    <t>kanczym@gmail.com</t>
+  </si>
+  <si>
+    <t>+36305322943</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -901,55 +916,55 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="26"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="26" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="20% - 1. jelölőszín" xfId="42" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 2. jelölőszín" xfId="1" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 3. jelölőszín" xfId="2" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 4. jelölőszín" xfId="3" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 5. jelölőszín" xfId="4" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 6. jelölőszín" xfId="5" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 1. jelölőszín" xfId="6" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 2. jelölőszín" xfId="7" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 3. jelölőszín" xfId="8" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 4. jelölőszín" xfId="9" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 5. jelölőszín" xfId="10" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 6. jelölőszín" xfId="11" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 1. jelölőszín" xfId="12" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 2. jelölőszín" xfId="13" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 3. jelölőszín" xfId="14" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 4. jelölőszín" xfId="15" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 5. jelölőszín" xfId="16" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 6. jelölőszín" xfId="17" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Bevitel" xfId="18" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Cím" xfId="19" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Címsor 1" xfId="20" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Címsor 2" xfId="21" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Címsor 3" xfId="22" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Címsor 4" xfId="23" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Ellenőrzőcella" xfId="24" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Figyelmeztetés" xfId="25" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Hivatkozás" xfId="26" builtinId="8"/>
-    <cellStyle name="Hivatkozott cella" xfId="27" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Jegyzet" xfId="28" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Jelölőszín 1" xfId="29" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Jelölőszín 2" xfId="30" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Jelölőszín 3" xfId="31" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Jelölőszín 4" xfId="32" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Jelölőszín 5" xfId="33" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Jelölőszín 6" xfId="34" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Jó" xfId="35" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Kimenet" xfId="36" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Magyarázó szöveg" xfId="37" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Normál" xfId="0" builtinId="0"/>
-    <cellStyle name="Összesen" xfId="38" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Rossz" xfId="39" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Semleges" xfId="40" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Számítás" xfId="41" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="42" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="1" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="2" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="3" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="4" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="5" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="6" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="7" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="8" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="10" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="11" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="12" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="14" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="15" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="16" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="17" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="29" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="30" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="31" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="32" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="33" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="34" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="39" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="41" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="24" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="37" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="35" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="20" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="21" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="22" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="23" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="26" builtinId="8"/>
+    <cellStyle name="Input" xfId="18" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="27" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="40" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="28" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="36" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="19" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="38" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="25" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -964,13 +979,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E04BEC9-A6A9-4700-BB84-8D7EEEAA9D6D}" name="Táblázat1" displayName="Táblázat1" ref="A1:G34" totalsRowShown="0">
-  <autoFilter ref="A1:G34" xr:uid="{4E04BEC9-A6A9-4700-BB84-8D7EEEAA9D6D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E04BEC9-A6A9-4700-BB84-8D7EEEAA9D6D}" name="Táblázat1" displayName="Táblázat1" ref="A1:G35" totalsRowShown="0">
+  <autoFilter ref="A1:G35" xr:uid="{4E04BEC9-A6A9-4700-BB84-8D7EEEAA9D6D}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{20F74619-F6C6-402B-976F-3EB6D6C2561B}" name="Id"/>
     <tableColumn id="2" xr3:uid="{141F81C0-34A9-4FDB-B97E-1F75C52CCC3F}" name="Név"/>
@@ -1301,734 +1312,840 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D74237-402A-451B-B92A-B4098F765610}">
-  <dimension ref="A1:O34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <v>36308415372</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="3">
         <v>36204446001</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="3">
         <v>36202309780</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>36309595631</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="3">
         <v>36307225044</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="3">
         <v>36307260808</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="3">
         <v>36306557189</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="3">
         <v>36301355402</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="3">
         <v>36205175033</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="3">
         <v>36202799322</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="3">
         <v>36305869332</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="3">
         <v>36304001670</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="3">
         <v>36308838715</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="3">
         <v>36703134683</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+    <row r="18" spans="1:7">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="3">
         <v>36308503919</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+    <row r="19" spans="1:7">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="3">
         <v>36303332466</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+    <row r="20" spans="1:7">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="3">
         <v>36303332466</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+    <row r="21" spans="1:7">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>67</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="3">
         <v>36709679051</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+    <row r="22" spans="1:7">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+    <row r="23" spans="1:7">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2" t="s">
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+    <row r="24" spans="1:7">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+    <row r="25" spans="1:7">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2" t="s">
+      <c r="E25" s="3"/>
+      <c r="F25" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+    <row r="26" spans="1:7">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+    <row r="27" spans="1:7">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2" t="s">
+      <c r="E27" s="3"/>
+      <c r="F27" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+    <row r="28" spans="1:7">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+    <row r="29" spans="1:7">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+    <row r="30" spans="1:7">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+    <row r="31" spans="1:7">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2" t="s">
+      <c r="E31" s="3"/>
+      <c r="F31" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+    <row r="32" spans="1:7">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="3">
+        <v>991</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="G33" s="3">
+        <v>36202130597</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="2">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="3">
+        <v>992</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>996</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G33" s="2">
-        <v>3630777777</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>997</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G34" s="2">
-        <v>36202130597</v>
+      <c r="D35" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2036,10 +2153,11 @@
     <hyperlink ref="F12" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="F17" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="F21" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F34" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/ugyfelek_adat.xlsx
+++ b/data/ugyfelek_adat.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/595ecd328626fcde/munka/ugyfelek/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="8_{E8C6EC21-E844-4967-91C2-3ADAEC31A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E817F8E3-E009-44D1-8BBC-6F1727CEBB7C}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="8_{E8C6EC21-E844-4967-91C2-3ADAEC31A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD041447-3A9D-470B-A3BC-BEE16706A10C}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1275" windowWidth="21000" windowHeight="11625" xr2:uid="{66F20849-4EC5-42B8-B876-1042B778AFA7}"/>
+    <workbookView xWindow="1470" yWindow="1275" windowWidth="21000" windowHeight="11625" xr2:uid="{66F20849-4EC5-42B8-B876-1042B778AFA7}"/>
   </bookViews>
   <sheets>
     <sheet name="ugyfelek_adat" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t>Id</t>
   </si>
@@ -423,12 +423,40 @@
   </si>
   <si>
     <t>+36305322943</t>
+  </si>
+  <si>
+    <t>Bori Katalin</t>
+  </si>
+  <si>
+    <t>Csaba utca 22/B</t>
+  </si>
+  <si>
+    <t>2 em. 6.csengő</t>
+  </si>
+  <si>
+    <t>kbk70@freemail.hu</t>
+  </si>
+  <si>
+    <t>+36204070080</t>
+  </si>
+  <si>
+    <t>Fazekas-Csanádi Viktória</t>
+  </si>
+  <si>
+    <t>Déva utca 8</t>
+  </si>
+  <si>
+    <t>csanadi.viktoria1@gmail.com</t>
+  </si>
+  <si>
+    <t>+36308520547</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="19">
     <font>
       <sz val="11"/>
@@ -871,100 +899,142 @@
     </border>
   </borders>
   <cellStyleXfs count="43">
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0"/>
+    <xf fontId="1" fillId="10" borderId="0"/>
+    <xf fontId="1" fillId="14" borderId="0"/>
+    <xf fontId="1" fillId="18" borderId="0"/>
+    <xf fontId="1" fillId="22" borderId="0"/>
+    <xf fontId="1" fillId="26" borderId="0"/>
+    <xf fontId="1" fillId="30" borderId="0"/>
+    <xf fontId="1" fillId="11" borderId="0"/>
+    <xf fontId="1" fillId="15" borderId="0"/>
+    <xf fontId="1" fillId="19" borderId="0"/>
+    <xf fontId="1" fillId="23" borderId="0"/>
+    <xf fontId="1" fillId="27" borderId="0"/>
+    <xf fontId="1" fillId="31" borderId="0"/>
+    <xf fontId="1" fillId="12" borderId="0"/>
+    <xf fontId="1" fillId="16" borderId="0"/>
+    <xf fontId="1" fillId="20" borderId="0"/>
+    <xf fontId="1" fillId="24" borderId="0"/>
+    <xf fontId="1" fillId="28" borderId="0"/>
+    <xf fontId="1" fillId="32" borderId="0"/>
+    <xf fontId="9" fillId="5" borderId="4"/>
+    <xf fontId="2" fillId="0" borderId="0"/>
+    <xf fontId="3" fillId="0" borderId="1"/>
+    <xf fontId="4" fillId="0" borderId="2"/>
+    <xf fontId="5" fillId="0" borderId="3"/>
+    <xf fontId="5" fillId="0" borderId="0"/>
+    <xf fontId="13" fillId="7" borderId="7"/>
+    <xf fontId="14" fillId="0" borderId="0"/>
+    <xf fontId="18" fillId="10" borderId="0"/>
+    <xf fontId="12" fillId="0" borderId="6"/>
+    <xf fontId="1" fillId="8" borderId="8"/>
+    <xf fontId="17" fillId="9" borderId="0"/>
+    <xf fontId="17" fillId="13" borderId="0"/>
+    <xf fontId="17" fillId="17" borderId="0"/>
+    <xf fontId="17" fillId="21" borderId="0"/>
+    <xf fontId="17" fillId="25" borderId="0"/>
+    <xf fontId="17" fillId="29" borderId="0"/>
+    <xf fontId="6" fillId="2" borderId="0"/>
+    <xf fontId="10" fillId="6" borderId="5"/>
+    <xf fontId="15" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="10" borderId="0"/>
+    <xf fontId="16" fillId="0" borderId="9"/>
+    <xf fontId="7" fillId="3" borderId="0"/>
+    <xf fontId="8" fillId="4" borderId="0"/>
+    <xf fontId="11" fillId="6" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="26" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="46">
+    <xf fontId="1" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf fontId="1" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="1"/>
+    <xf fontId="1" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="2"/>
+    <xf fontId="1" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="3"/>
+    <xf fontId="1" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="4"/>
+    <xf fontId="1" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="5"/>
+    <xf fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="6"/>
+    <xf fontId="1" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="7"/>
+    <xf fontId="1" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="8"/>
+    <xf fontId="1" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="9"/>
+    <xf fontId="1" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="10"/>
+    <xf fontId="1" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="11"/>
+    <xf fontId="1" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="12"/>
+    <xf fontId="1" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="13"/>
+    <xf fontId="1" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="14"/>
+    <xf fontId="1" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="15"/>
+    <xf fontId="1" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="16"/>
+    <xf fontId="1" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="17"/>
+    <xf fontId="9" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" xfId="18"/>
+    <xf fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="19"/>
+    <xf fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="20"/>
+    <xf fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="21"/>
+    <xf fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="22"/>
+    <xf fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="23"/>
+    <xf fontId="13" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" xfId="24"/>
+    <xf fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="25"/>
+    <xf fontId="18" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26"/>
+    <xf fontId="12" applyFont="1" fillId="0" applyFill="1" borderId="6" applyBorder="1" xfId="27"/>
+    <xf fontId="1" applyFont="1" fillId="8" applyFill="1" borderId="8" applyBorder="1" xfId="28"/>
+    <xf fontId="17" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="29"/>
+    <xf fontId="17" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="30"/>
+    <xf fontId="17" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="31"/>
+    <xf fontId="17" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="32"/>
+    <xf fontId="17" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="33"/>
+    <xf fontId="17" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="34"/>
+    <xf fontId="6" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="35"/>
+    <xf fontId="10" applyFont="1" fillId="6" applyFill="1" borderId="5" applyBorder="1" xfId="36"/>
+    <xf fontId="15" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="37"/>
+    <xf fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="38"/>
+    <xf fontId="16" applyFont="1" fillId="0" applyFill="1" borderId="9" applyBorder="1" xfId="39"/>
+    <xf fontId="7" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="40"/>
+    <xf fontId="8" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="41"/>
+    <xf fontId="11" applyFont="1" fillId="6" applyFill="1" borderId="4" applyBorder="1" xfId="42"/>
+    <xf fontId="1" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf fontId="1" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="38"/>
+    <xf fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="38"/>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="20% - Accent1" xfId="42" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="1" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="2" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="3" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="4" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="5" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="6" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="7" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="8" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="10" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="11" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="12" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="14" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="15" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="16" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="17" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="29" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="30" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="31" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="32" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="33" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="34" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="39" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="41" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="24" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="37" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="35" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="20" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="21" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="22" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="23" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="26" builtinId="8"/>
-    <cellStyle name="Input" xfId="18" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="27" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="40" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="28" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="36" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="19" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="38" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="25" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="20% - 1. jelölőszín" xfId="0" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 2. jelölőszín" xfId="1" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 3. jelölőszín" xfId="2" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 4. jelölőszín" xfId="3" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 5. jelölőszín" xfId="4" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 6. jelölőszín" xfId="5" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 1. jelölőszín" xfId="6" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 2. jelölőszín" xfId="7" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 3. jelölőszín" xfId="8" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 4. jelölőszín" xfId="9" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 5. jelölőszín" xfId="10" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 6. jelölőszín" xfId="11" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 1. jelölőszín" xfId="12" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 2. jelölőszín" xfId="13" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 3. jelölőszín" xfId="14" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 4. jelölőszín" xfId="15" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 5. jelölőszín" xfId="16" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 6. jelölőszín" xfId="17" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bevitel" xfId="18" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Cím" xfId="19" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Címsor 1" xfId="20" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Címsor 2" xfId="21" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Címsor 3" xfId="22" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Címsor 4" xfId="23" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Ellenőrzőcella" xfId="24" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Figyelmeztetés" xfId="25" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Hivatkozás" xfId="26" builtinId="8"/>
+    <cellStyle name="Hivatkozott cella" xfId="27" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Jegyzet" xfId="28" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Jelölőszín 1" xfId="29" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Jelölőszín 2" xfId="30" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Jelölőszín 3" xfId="31" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Jelölőszín 4" xfId="32" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Jelölőszín 5" xfId="33" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Jelölőszín 6" xfId="34" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Jó" xfId="35" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Kimenet" xfId="36" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Magyarázó szöveg" xfId="37" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Normál" xfId="38" builtinId="0"/>
+    <cellStyle name="Összesen" xfId="39" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Rossz" xfId="40" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Semleges" xfId="41" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Számítás" xfId="42" builtinId="22" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -979,9 +1049,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E04BEC9-A6A9-4700-BB84-8D7EEEAA9D6D}" name="Táblázat1" displayName="Táblázat1" ref="A1:G35" totalsRowShown="0">
-  <autoFilter ref="A1:G35" xr:uid="{4E04BEC9-A6A9-4700-BB84-8D7EEEAA9D6D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E04BEC9-A6A9-4700-BB84-8D7EEEAA9D6D}" name="Táblázat1" displayName="Táblázat1" ref="A1:G38" totalsRowShown="0">
+  <autoFilter ref="A1:G38" xr:uid="{4E04BEC9-A6A9-4700-BB84-8D7EEEAA9D6D}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{20F74619-F6C6-402B-976F-3EB6D6C2561B}" name="Id"/>
     <tableColumn id="2" xr3:uid="{141F81C0-34A9-4FDB-B97E-1F75C52CCC3F}" name="Név"/>
@@ -1312,848 +1386,815 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D74237-402A-451B-B92A-B4098F765610}">
-  <dimension ref="A1:O35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1" style="44"/>
+    <col min="2" max="2" bestFit="1" width="19" customWidth="1" style="44"/>
+    <col min="3" max="3" bestFit="1" width="14.42578125" customWidth="1" style="44"/>
+    <col min="4" max="4" bestFit="1" width="21.5703125" customWidth="1" style="44"/>
+    <col min="5" max="5" width="14" customWidth="1" style="44"/>
+    <col min="6" max="6" bestFit="1" width="25.85546875" customWidth="1" style="44"/>
+    <col min="7" max="7" bestFit="1" width="13.42578125" customWidth="1" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="3" t="s">
+    <row r="1">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="3">
+    </row>
+    <row r="2">
+      <c r="A2" s="45">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="45">
         <v>36308415372</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="3">
+    </row>
+    <row r="3">
+      <c r="A3" s="45">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="45">
         <v>36204446001</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="3">
+    </row>
+    <row r="4">
+      <c r="A4" s="45">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="45">
         <v>36202309780</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="3">
+    </row>
+    <row r="5">
+      <c r="A5" s="45">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="45"/>
+      <c r="F5" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="45">
         <v>36309595631</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="3">
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="45">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="45">
         <v>36307225044</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="3">
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="45">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="45"/>
+      <c r="F7" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="45">
         <v>36307260808</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="3">
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="45">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
+      <c r="E8" s="45"/>
+      <c r="F8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="45">
         <v>36306557189</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="3">
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="45"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="45">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
+      <c r="E9" s="45"/>
+      <c r="F9" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="45">
         <v>36301355402</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="3">
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="45"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="45">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="3">
+      <c r="J10" s="45"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="45"/>
+      <c r="M10" s="45"/>
+      <c r="N10" s="45"/>
+      <c r="O10" s="45"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="3">
+      <c r="G11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="45"/>
+      <c r="M11" s="45"/>
+      <c r="N11" s="45"/>
+      <c r="O11" s="45"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="45">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="45">
         <v>36205175033</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="3">
+    </row>
+    <row r="13">
+      <c r="A13" s="45">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="45">
         <v>36202799322</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="3">
+    </row>
+    <row r="14">
+      <c r="A14" s="45">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="45">
         <v>36305869332</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="3">
+    </row>
+    <row r="15">
+      <c r="A15" s="45">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="45">
         <v>36304001670</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="3">
+    </row>
+    <row r="16">
+      <c r="A16" s="45">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="45">
         <v>36308838715</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="3">
+    </row>
+    <row r="17">
+      <c r="A17" s="45">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="45">
         <v>36703134683</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="3">
+    <row r="18">
+      <c r="A18" s="45">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="45">
         <v>36308503919</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="3">
+    <row r="19">
+      <c r="A19" s="45">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="45">
         <v>36303332466</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="3">
+    <row r="20">
+      <c r="A20" s="45">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="45">
         <v>36303332466</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="3">
+    <row r="21">
+      <c r="A21" s="45">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="45">
         <v>36709679051</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="3">
+    <row r="22">
+      <c r="A22" s="45">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="45" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="3">
+    <row r="23">
+      <c r="A23" s="45">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
+      <c r="E23" s="45"/>
+      <c r="F23" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="45" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="3">
+    <row r="24">
+      <c r="A24" s="45">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="45" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="3">
+    <row r="25">
+      <c r="A25" s="45">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3" t="s">
+      <c r="E25" s="45"/>
+      <c r="F25" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="45" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="3">
+    <row r="26">
+      <c r="A26" s="45">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="45" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="3">
+    <row r="27">
+      <c r="A27" s="45">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3" t="s">
+      <c r="E27" s="45"/>
+      <c r="F27" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="45" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="3">
+    <row r="28">
+      <c r="A28" s="45">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="45" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="3">
+    <row r="29">
+      <c r="A29" s="45">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3" t="s">
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="45" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="3">
+    <row r="30">
+      <c r="A30" s="45">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="45" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="3">
+    <row r="31">
+      <c r="A31" s="45">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3" t="s">
+      <c r="E31" s="45"/>
+      <c r="F31" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="45" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="3">
+    <row r="32">
+      <c r="A32" s="45">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="3">
+      <c r="G32" s="45"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="45">
         <v>991</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3" t="s">
+      <c r="E33" s="45"/>
+      <c r="F33" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="45">
         <v>36202130597</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="2">
+    <row r="34">
+      <c r="A34" s="44">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="26" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="3">
+    <row r="35">
+      <c r="A35" s="45">
         <v>992</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="45" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="45"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="45">
+        <v>993</v>
+      </c>
+      <c r="B37" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="F37" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37" s="45" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="45">
+        <v>994</v>
+      </c>
+      <c r="B38" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="G38" s="45" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F12" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F17" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F21" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F34" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F12" r:id="rId9"/>
+    <hyperlink ref="F17" r:id="rId10"/>
+    <hyperlink ref="F21" r:id="rId11"/>
+    <hyperlink ref="F34" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
